--- a/tests/fixtures/elm-court/client.xlsx
+++ b/tests/fixtures/elm-court/client.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="21">
   <si>
     <t>Elm Court — Rent Roll</t>
   </si>
@@ -44,6 +44,9 @@
   </si>
   <si>
     <t>Rent Steps</t>
+  </si>
+  <si>
+    <t>% Rent</t>
   </si>
   <si>
     <t>110</t>
@@ -447,10 +450,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -475,8 +478,11 @@
       <c r="H1" t="s">
         <v>1</v>
       </c>
+      <c r="I1" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -501,8 +507,11 @@
       <c r="H2" t="s">
         <v>1</v>
       </c>
+      <c r="I2" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -527,56 +536,65 @@
       <c r="H4" t="s">
         <v>10</v>
       </c>
+      <c r="I4" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5">
         <v>8000</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5">
         <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
         <v>1</v>
       </c>
+      <c r="I5" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6">
         <v>1000</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6">
         <v>55</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" t="s">
         <v>1</v>
       </c>
     </row>
